--- a/output/pdf_financials_xlsx/AYA.xlsx
+++ b/output/pdf_financials_xlsx/AYA.xlsx
@@ -1435,7 +1435,7 @@
         <v>0.353194</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.396948</v>
+        <v>-7.375782</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.433576</v>
@@ -1688,25 +1688,25 @@
         <v>-1.407159</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.840681</v>
+        <v>-2.840681</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.281265</v>
+        <v>-2.281265</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.489417</v>
+        <v>-3.489417</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>14.856325</v>
+        <v>-14.856325</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>8.655961</v>
+        <v>-8.655961</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.529035</v>
+        <v>-4.529035</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.162612</v>
+        <v>-2.162612</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-2.663826</v>
@@ -1883,25 +1883,25 @@
         <v>-1.407159</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.840681</v>
+        <v>-2.840681</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.281265</v>
+        <v>-2.281265</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.489417</v>
+        <v>-3.489417</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>14.856325</v>
+        <v>-14.856325</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>8.655961</v>
+        <v>-8.655961</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>4.529035</v>
+        <v>-4.529035</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2.162612</v>
+        <v>-2.162612</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-2.663826</v>
@@ -2116,13 +2116,13 @@
         <v>28.14318</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>47.344683</v>
+        <v>-47.344683</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>76.04216700000001</v>
+        <v>-76.04216700000001</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>116.3139</v>
+        <v>-116.3139</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>13.40669943999888</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>10.21386308285506</v>
+        <v>189.7861369171449</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>2.835701813896637</v>
@@ -68117,28 +68117,28 @@
         </is>
       </c>
       <c r="H569" s="5" t="n">
-        <v>2.840681</v>
+        <v>-2.840681</v>
       </c>
       <c r="I569" s="5" t="n">
-        <v>2.281265</v>
+        <v>-2.281265</v>
       </c>
       <c r="J569" s="5" t="n">
-        <v>3.489417</v>
+        <v>-3.489417</v>
       </c>
       <c r="K569" s="5" t="n">
-        <v>14.856325</v>
+        <v>-14.856325</v>
       </c>
       <c r="L569" s="5" t="n">
-        <v>8.655961</v>
+        <v>-8.655961</v>
       </c>
       <c r="M569" s="5" t="n">
-        <v>4.529035</v>
+        <v>-4.529035</v>
       </c>
       <c r="N569" s="5" t="n">
-        <v>2.162612</v>
+        <v>-2.162612</v>
       </c>
       <c r="O569" s="5" t="n">
-        <v>3.422255</v>
+        <v>-3.422255</v>
       </c>
       <c r="P569" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AYA.xlsx
+++ b/output/pdf_financials_xlsx/AYA.xlsx
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011907</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001748</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.418113</v>
+        <v>-0.406206</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.19656</v>
+        <v>-2.194812</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.422159</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.418113</v>
+        <v>-0.406206</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.19656</v>
+        <v>-2.194812</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.415507</v>
@@ -2639,22 +2639,22 @@
         <v>0.15741</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.138588</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.376327</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.266854</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>7.063991</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>5.619275</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>19.000163</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>30.533399</v>
@@ -2761,22 +2761,22 @@
         <v>0.332983</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.112839</v>
+        <v>2.251427</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.051776</v>
+        <v>0.428103</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.266854</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>7.063991</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>5.619275</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>19.000163</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>30.533399</v>
@@ -3493,22 +3493,22 @@
         <v>0.091206</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.19122</v>
+        <v>1.052632</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.592722</v>
+        <v>1.216395</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.633282</v>
+        <v>1.366428</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>8.668823</v>
+        <v>1.604832</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>6.87636</v>
+        <v>1.257085</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>20.058428</v>
+        <v>1.058265</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>2.163186</v>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -19352,7 +19352,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -60398,7 +60398,11 @@
           <t>General and administrative expenses (Note 18)(2)</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -79394,7 +79398,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E677" s="5" t="n">

--- a/output/pdf_financials_xlsx/AYA.xlsx
+++ b/output/pdf_financials_xlsx/AYA.xlsx
@@ -2284,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>3.198076</v>
       </c>
       <c r="P28" s="1" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>-0.84205</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>5.117383</v>
+        <v>8.315459000000001</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>-6.091787072997051</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>14.91865147816533</v>
+        <v>24.24196795549076</v>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
@@ -6722,10 +6722,10 @@
         <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>3.198076</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>6.342209</v>
       </c>
       <c r="Q100" s="3" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.005453</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -41258,7 +41258,11 @@
           <t>Depreciation of property, plant, and equipment (Note 5)</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -56288,7 +56292,11 @@
           <t>Proceeds from disposal of property and equipment -</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
